--- a/data/nzd0072/nzd0072.xlsx
+++ b/data/nzd0072/nzd0072.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F336"/>
+  <dimension ref="A1:F338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8498,6 +8498,54 @@
         <v>368</v>
       </c>
       <c r="F336" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>369.2</v>
+      </c>
+      <c r="C337" t="n">
+        <v>365.78</v>
+      </c>
+      <c r="D337" t="n">
+        <v>360.7</v>
+      </c>
+      <c r="E337" t="n">
+        <v>369.47</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>370.11</v>
+      </c>
+      <c r="C338" t="n">
+        <v>367.16</v>
+      </c>
+      <c r="D338" t="n">
+        <v>362.26</v>
+      </c>
+      <c r="E338" t="n">
+        <v>370.56</v>
+      </c>
+      <c r="F338" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8514,7 +8562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B361"/>
+  <dimension ref="A1:B363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12127,6 +12175,26 @@
       </c>
       <c r="B361" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>0.46</v>
       </c>
     </row>
   </sheetData>
@@ -12295,28 +12363,28 @@
         <v>0.1137</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007355064042428746</v>
+        <v>0.004554889026440787</v>
       </c>
       <c r="J2" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K2" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001878101408849808</v>
+        <v>7.294757151188325e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.991673798031279</v>
+        <v>2.985248962692378</v>
       </c>
       <c r="N2" t="n">
-        <v>15.39724768529455</v>
+        <v>15.33599999944546</v>
       </c>
       <c r="O2" t="n">
-        <v>3.923932681035003</v>
+        <v>3.916120529228571</v>
       </c>
       <c r="P2" t="n">
-        <v>371.685019445494</v>
+        <v>371.7149824632889</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12377,28 +12445,28 @@
         <v>0.1536</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1232670497399044</v>
+        <v>0.1175113130010486</v>
       </c>
       <c r="J3" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K3" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04948514442421081</v>
+        <v>0.04545778715258209</v>
       </c>
       <c r="M3" t="n">
-        <v>2.541379383703114</v>
+        <v>2.549326929169382</v>
       </c>
       <c r="N3" t="n">
-        <v>15.60446416176544</v>
+        <v>15.63670436089459</v>
       </c>
       <c r="O3" t="n">
-        <v>3.950248620247267</v>
+        <v>3.954327295621164</v>
       </c>
       <c r="P3" t="n">
-        <v>367.7388389671394</v>
+        <v>367.8004291419545</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12459,28 +12527,28 @@
         <v>0.1256</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05952358483830607</v>
+        <v>0.05633059547075658</v>
       </c>
       <c r="J4" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K4" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01002452048914937</v>
+        <v>0.00909774405442465</v>
       </c>
       <c r="M4" t="n">
-        <v>3.00924258813765</v>
+        <v>3.004501922731404</v>
       </c>
       <c r="N4" t="n">
-        <v>18.70724257369505</v>
+        <v>18.63737767728377</v>
       </c>
       <c r="O4" t="n">
-        <v>4.325186998696709</v>
+        <v>4.317102926417641</v>
       </c>
       <c r="P4" t="n">
-        <v>362.4258309501129</v>
+        <v>362.459995786033</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12541,28 +12609,28 @@
         <v>0.1067</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1197464456327866</v>
+        <v>0.1199412803648927</v>
       </c>
       <c r="J5" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K5" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03863749356985602</v>
+        <v>0.03929990698122476</v>
       </c>
       <c r="M5" t="n">
-        <v>3.114309076205331</v>
+        <v>3.099164625275313</v>
       </c>
       <c r="N5" t="n">
-        <v>19.07542783064012</v>
+        <v>18.964119824713</v>
       </c>
       <c r="O5" t="n">
-        <v>4.367542539076194</v>
+        <v>4.354781260260152</v>
       </c>
       <c r="P5" t="n">
-        <v>366.6438612255914</v>
+        <v>366.641773132633</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12604,7 +12672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F336"/>
+  <dimension ref="A1:F338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23359,6 +23427,70 @@
         </is>
       </c>
     </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>-35.43041908069118,174.36112041842784</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>-35.43114377899466,174.3610114204538</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>-35.431875685129704,174.36103354285632</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>-35.43258931914891,174.36125351787223</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>-35.43041965595739,174.3611304170693</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>-35.431143617162164,174.36102661949616</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>-35.43187397498715,174.36105059847662</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-35.432587873243676,174.36126539345506</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0072/nzd0072.xlsx
+++ b/data/nzd0072/nzd0072.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F338"/>
+  <dimension ref="A1:F339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8546,6 +8546,30 @@
         <v>370.56</v>
       </c>
       <c r="F338" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="C339" t="n">
+        <v>370.84</v>
+      </c>
+      <c r="D339" t="n">
+        <v>362.94</v>
+      </c>
+      <c r="E339" t="n">
+        <v>371.76</v>
+      </c>
+      <c r="F339" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8562,7 +8586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B363"/>
+  <dimension ref="A1:B364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12195,6 +12219,16 @@
       </c>
       <c r="B363" t="n">
         <v>0.46</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -12363,28 +12397,28 @@
         <v>0.1137</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004554889026440787</v>
+        <v>0.005668908750091613</v>
       </c>
       <c r="J2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L2" t="n">
-        <v>7.294757151188325e-05</v>
+        <v>0.000113742451692378</v>
       </c>
       <c r="M2" t="n">
-        <v>2.985248962692378</v>
+        <v>2.98233717850107</v>
       </c>
       <c r="N2" t="n">
-        <v>15.33599999944546</v>
+        <v>15.29986487380461</v>
       </c>
       <c r="O2" t="n">
-        <v>3.916120529228571</v>
+        <v>3.911504170239962</v>
       </c>
       <c r="P2" t="n">
-        <v>371.7149824632889</v>
+        <v>371.703015926529</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12445,28 +12479,28 @@
         <v>0.1536</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1175113130010486</v>
+        <v>0.1174336997961657</v>
       </c>
       <c r="J3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04545778715258209</v>
+        <v>0.04571558603466941</v>
       </c>
       <c r="M3" t="n">
-        <v>2.549326929169382</v>
+        <v>2.542092073987813</v>
       </c>
       <c r="N3" t="n">
-        <v>15.63670436089459</v>
+        <v>15.59048676006026</v>
       </c>
       <c r="O3" t="n">
-        <v>3.954327295621164</v>
+        <v>3.948479043892757</v>
       </c>
       <c r="P3" t="n">
-        <v>367.8004291419545</v>
+        <v>367.8012628446704</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12527,28 +12561,28 @@
         <v>0.1256</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05633059547075658</v>
+        <v>0.05567665199835429</v>
       </c>
       <c r="J4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00909774405442465</v>
+        <v>0.008952185752015063</v>
       </c>
       <c r="M4" t="n">
-        <v>3.004501922731404</v>
+        <v>2.998260890779042</v>
       </c>
       <c r="N4" t="n">
-        <v>18.63737767728377</v>
+        <v>18.58542065159811</v>
       </c>
       <c r="O4" t="n">
-        <v>4.317102926417641</v>
+        <v>4.311081146487283</v>
       </c>
       <c r="P4" t="n">
-        <v>362.459995786033</v>
+        <v>362.4670202923637</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12609,28 +12643,28 @@
         <v>0.1067</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1199412803648927</v>
+        <v>0.1211240759516401</v>
       </c>
       <c r="J5" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K5" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03929990698122476</v>
+        <v>0.04030597064555197</v>
       </c>
       <c r="M5" t="n">
-        <v>3.099164625275313</v>
+        <v>3.096240379813481</v>
       </c>
       <c r="N5" t="n">
-        <v>18.964119824713</v>
+        <v>18.91842642938201</v>
       </c>
       <c r="O5" t="n">
-        <v>4.354781260260152</v>
+        <v>4.349531748289924</v>
       </c>
       <c r="P5" t="n">
-        <v>366.641773132633</v>
+        <v>366.6290678217954</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12672,7 +12706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F338"/>
+  <dimension ref="A1:F339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23491,6 +23525,38 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>-35.43042186851199,174.36116887338372</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>-35.43114318559951,174.3610671502752</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>-35.43187322953965,174.36105803297755</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-35.43258628142008,174.36127846749068</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
